--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260923.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.83%</t>
+          <t>11.87%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.51%</t>
+          <t>10.65%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>PWR US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>廣達服務公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>89,925</t>
+          <t>35,355</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.88%</t>
+          <t>7.85%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PWR US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>廣達服務公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>35,355</t>
+          <t>89,925</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.85%</t>
+          <t>7.83%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.24%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.70%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>112,066</t>
+          <t>58,659</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>58,659</t>
+          <t>112,066</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1151,44 +1151,44 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>50,910</t>
+          <t>27,369</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,369</t>
+          <t>50,910</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1217,61 +1217,61 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,237</t>
+          <t>8,904</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>74,774</t>
+          <t>11,237</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>8,904</t>
+          <t>74,774</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1386,46 +1386,46 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>145,345</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>145,345</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>43,283</t>
+          <t>25,581</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>25,581</t>
+          <t>5,778</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,22 +1481,22 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5,778</t>
+          <t>43,283</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1628,51 +1628,51 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,921</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,839</t>
+          <t>7,921</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>124,089,086</t>
+          <t>123,315,658</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
